--- a/excel/铝.xlsx
+++ b/excel/铝.xlsx
@@ -1003,19 +1003,15 @@
         <f>IF(AND(ISNUMBER(R5),ISNUMBER(M5),M5&lt;&gt;0),(R5-M5)/M5,"-")</f>
         <v/>
       </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T5" s="2" t="n">
+        <v>545.25</v>
       </c>
       <c r="U5" s="5">
         <f>IF(AND(ISNUMBER(T5),ISNUMBER(N5),N5&lt;&gt;0),(T5-N5)/N5,"-")</f>
         <v/>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V5" s="2" t="n">
+        <v>545.25</v>
       </c>
       <c r="W5" s="5">
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
@@ -1023,7 +1019,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>2024 +18.8%、2025 +16.2%：几内亚 CBK（Kindia）和 Dian-Dian 矿区扩产驱动，属真实增量</t>
+          <t>2026H1（8/19 港交所中报）：铝土矿产量 1,090.5 万湿吨（+12.8%）——半年口径，季度不拆；26Q1 未披露，Q1=Q2=H1/2=545.25 拟合。源：RUSAL 2026 中期业绩（HKEX 2026-08-19）</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1033,7 +1029,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>2022 年起停发季报，仅半年度/年度披露（H1：23年675.4推算/24年794.0/25年966.8）；湿吨</t>
+          <t>2022 年起停发季报，仅半年度/年度披露（H1：23年675.4推算/24年794.0/25年966.8）；湿吨；2026H1=1,090.5（湿吨，HKEX 中报原文 Bauxite (wet) 10,905kt），Q1 未披露两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -1266,10 +1262,8 @@
         <f>IF(AND(ISNUMBER(T7),ISNUMBER(N7),N7&lt;&gt;0),(T7-N7)/N7,"-")</f>
         <v/>
       </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V7" s="2" t="n">
+        <v>182.9</v>
       </c>
       <c r="W7" s="5">
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
@@ -1277,7 +1271,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>FY26（2025.4–2026.3）开采 770.1 / 运输 770.7 均创纪录（运输 +6.13%）</t>
+          <t>Q1FY27(=26Q2)：铝土矿产量182.9万吨（官方演示稿Physical Performance；新闻稿开采口径195.2万吨创Q1纪录）</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1404,7 +1398,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026中报(8/27)未披露铝土矿产量（中铝半年报惯例不披露,年报才有）</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1752,14 +1746,18 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="W11" s="5">
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" s="3" t="n"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Ma'aden Q2 2026 已披露（铝板块收入+49%），但铝土矿分季产量未见公开披露 → 未找到。源：Ma'aden Q2 2026 / AlCircle 2026-08-11</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2427,19 +2425,15 @@
         <f>IF(AND(ISNUMBER(R5),ISNUMBER(M5),M5&lt;&gt;0),(R5-M5)/M5,"-")</f>
         <v/>
       </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T5" s="2" t="n">
+        <v>182.9</v>
       </c>
       <c r="U5" s="5">
         <f>IF(AND(ISNUMBER(T5),ISNUMBER(N5),N5&lt;&gt;0),(T5-N5)/N5,"-")</f>
         <v/>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V5" s="2" t="n">
+        <v>182.9</v>
       </c>
       <c r="W5" s="5">
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
@@ -2447,7 +2441,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>2024 +25.3%、2025 +6.7%：并表口径扩大（2024-04 起河北文丰 30%、2025-07 起印度 Pioneer 26%），非有机增长</t>
+          <t>2026H1（8/19 港交所中报）：氧化铝产量 365.8 万吨（+7.6%，增量主要来自 2025-07 收购的印度 Pioneer 氧化铝厂 26% 权益）——半年口径，季度不拆；26Q1 未披露，Q1=Q2=H1/2=182.9 拟合。源：RUSAL 2026 中期业绩（HKEX 2026-08-19）</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -2457,7 +2451,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>2022 年起停发季报，仅半年度/年度（H1：24年299.5/25年340.0）；同比分析须注意口径跳变</t>
+          <t>2022 年起停发季报，仅半年度/年度（H1：24年299.5/25年340.0）；同比分析须注意口径跳变；2026H1=365.8（HKEX 中报原文 Alumina 3,658kt），Q1 未披露两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2851,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>Utkal 爬坡/去瓶颈，FY25 创 385.7 万吨纪录后 FY26 小幅回落</t>
+          <t>Q1FY27（=26Q2）业绩 8/7 已发：仅披露铝上游出货量 335kt，氧化铝产量未在新闻稿披露 → 未披露。源：Hindalco Q1FY27 业绩新闻稿（2026-08-07）</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2973,10 +2967,8 @@
         <f>IF(AND(ISNUMBER(T10),ISNUMBER(N10),N10&lt;&gt;0),(T10-N10)/N10,"-")</f>
         <v/>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V10" s="2" t="n">
+        <v>57.7</v>
       </c>
       <c r="W10" s="5">
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
@@ -2984,7 +2976,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>FY26（2025.4–2026.3）焙烧氧化铝 227.5（+11.16%）创纪录</t>
+          <t>Q1FY27(=26Q2)：煅烧氧化铝57.7万吨（创Q1纪录；水合物57.8万吨）；官方新闻稿8/1+演示稿</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -3090,10 +3082,8 @@
         <f>IF(AND(ISNUMBER(T11),ISNUMBER(N11),N11&lt;&gt;0),(T11-N11)/N11,"-")</f>
         <v/>
       </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V11" s="2" t="n">
+        <v>333</v>
       </c>
       <c r="W11" s="5">
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
@@ -3101,7 +3091,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>2026Q1 -9.6%：推测为主动压减外销（外销量-15.5%）与结构优化（标注：推测）</t>
+          <t>2026中报(8/27)：H1冶金级氧化铝738万吨(-14.19%)−26Q1 405=333（推算）；另精细氧化铝H1 234万吨(+12.5%)</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -3226,7 +3216,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>2025 +10.05%：印尼项目+国内满产，自给有余下外销量大增 +27.9%</t>
+          <t>2026中报(8/21港交所)仅销量口径：氧化铝销量691.7万吨(H1,+8.6%)；产量年报才披露</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -3329,19 +3319,15 @@
         <f>IF(AND(ISNUMBER(R13),ISNUMBER(M13),M13&lt;&gt;0),(R13-M13)/M13,"-")</f>
         <v/>
       </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T13" s="2" t="n">
+        <v>32.5</v>
       </c>
       <c r="U13" s="5">
         <f>IF(AND(ISNUMBER(T13),ISNUMBER(N13),N13&lt;&gt;0),(T13-N13)/N13,"-")</f>
         <v/>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V13" s="2" t="n">
+        <v>32.5</v>
       </c>
       <c r="W13" s="5">
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
@@ -3349,7 +3335,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>2025 降至 130.36（年报未给原因，2026 目标同步降至约130）</t>
+          <t>2026中报(8/27)：H1氧化铝产量65万吨(-3%)；Q1未单独披露,记H1累计</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3359,7 +3345,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>半年报披露 H1（23H1 73.32 / 24H1 72.30 / 25H1 66.97）；季报不披露产量</t>
+          <t>半年报披露 H1（23H1 73.32 / 24H1 72.30 / 25H1 66.97）；季报不披露产量；2026中报H1累计65万吨，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -3452,19 +3438,15 @@
         <f>IF(AND(ISNUMBER(R14),ISNUMBER(M14),M14&lt;&gt;0),(R14-M14)/M14,"-")</f>
         <v/>
       </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T14" s="2" t="n">
+        <v>63.115</v>
       </c>
       <c r="U14" s="5">
         <f>IF(AND(ISNUMBER(T14),ISNUMBER(N14),N14&lt;&gt;0),(T14-N14)/N14,"-")</f>
         <v/>
       </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V14" s="2" t="n">
+        <v>63.115</v>
       </c>
       <c r="W14" s="5">
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
@@ -3472,7 +3454,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>2023 +37.6% 系靖西天桂 250 万吨项目全部投产；2025 +10.38%</t>
+          <t>2026中报(8/18)：H1氧化铝产量126.23万吨(+5%)</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3482,7 +3464,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>半年报披露 H1（23H1 102.33 / 24H1 109.30 / 25H1 119.99）；季报不披露产量｜2025年报：氧化铝毛利率9.7%(2025H1尚有14.6%，下半年走弱)</t>
+          <t>半年报披露 H1（23H1 102.33 / 24H1 109.30 / 25H1 119.99）；季报不披露产量｜2025年报：氧化铝毛利率9.7%(2025H1尚有14.6%，下半年走弱)；2026中报H1累计126.23万吨，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -3717,14 +3699,18 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="W16" s="5">
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
-      <c r="X16" s="3" t="n"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Ma'aden Q2 2026 已披露，但 Ras Al Khair 氧化铝分季产量未见公开披露（二手源 vision2030 称某季 47.8 万吨，口径待核）→ 未找到。源：Ma'aden Q2 2026 / AlCircle</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="n"/>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4392,19 +4378,15 @@
         <f>IF(AND(ISNUMBER(R5),ISNUMBER(M5),M5&lt;&gt;0),(R5-M5)/M5,"-")</f>
         <v/>
       </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T5" s="2" t="n">
+        <v>100.5</v>
       </c>
       <c r="U5" s="5">
         <f>IF(AND(ISNUMBER(T5),ISNUMBER(N5),N5&lt;&gt;0),(T5-N5)/N5,"-")</f>
         <v/>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V5" s="2" t="n">
+        <v>100.5</v>
       </c>
       <c r="W5" s="5">
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
@@ -4412,7 +4394,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>2025 -1.9%：计划性产能优化（氧化铝成本高企，主动压减低效产能）</t>
+          <t>2026H1（8/19 港交所中报）：原铝产量 2.010 百万吨（+4.5%）——半年口径，季度不拆。源：RUSAL 2026 中期业绩（HKEX 2026-08-19）</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -4422,7 +4404,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>2022 年起停发季报，仅半年度/年度（H1：23年191.3推算/24年195.7/25年192.4）；注意 2025 销量大增系去库存，与产量走势背离，勿混用</t>
+          <t>2022 年起停发季报，仅半年度/年度（H1：23年191.3推算/24年195.7/25年192.4）；注意 2025 销量大增系去库存，与产量走势背离，勿混用；2026中报(8/19港交所)H1原铝201.0万吨(+4.5%)，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4906,7 @@
         <v>33</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>33.2</v>
+        <v>32.5</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>33.6</v>
@@ -4946,10 +4928,8 @@
         <f>IF(AND(ISNUMBER(T10),ISNUMBER(N10),N10&lt;&gt;0),(T10-N10)/N10,"-")</f>
         <v/>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V10" s="2" t="n">
+        <v>33.5</v>
       </c>
       <c r="W10" s="5">
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
@@ -4957,7 +4937,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>产能封顶（约133万吨/年），各季 ±2% 内波动</t>
+          <t>Q1FY27（=26Q2）铝上游出货量 335kt=33.5 万吨（同比+3%，出货量口径）；上游 EBITDA 创纪录 ₹7,390  crore（+81%）；Aditya 二期 FY28 投产。源：Hindalco Q1FY27 业绩新闻稿（2026-08-07）</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -5071,10 +5051,8 @@
         <f>IF(AND(ISNUMBER(T11),ISNUMBER(N11),N11&lt;&gt;0),(T11-N11)/N11,"-")</f>
         <v/>
       </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V11" s="2" t="n">
+        <v>11.6</v>
       </c>
       <c r="W11" s="5">
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
@@ -5082,7 +5060,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>FY26（2025.4–2026.3）47.2（+2.61%）创纪录</t>
+          <t>Q1FY27(=26Q2)：电解铝11.6万吨（上年同季11.5）；官方演示稿</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -5188,10 +5166,8 @@
         <f>IF(AND(ISNUMBER(T12),ISNUMBER(N12),N12&lt;&gt;0),(T12-N12)/N12,"-")</f>
         <v/>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V12" s="2" t="n">
+        <v>201</v>
       </c>
       <c r="W12" s="5">
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
@@ -5199,7 +5175,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>2024 +12.1%、2025 +6.2%：华云三期、青海600kA、广西华昇二期等重点项目投产+产能利用率提升；2026Q1 +3.6%</t>
+          <t>2026中报(8/27)：H1原铝(含合金)402万吨(+1.26%)−26Q1 201=201（推算）</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -5322,7 +5298,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>合规产能 646 万吨已基本满产（产量天花板）；增量在云南转移产能（2026 年底规划约300万吨）</t>
+          <t>2026中报(8/21港交所)仅销量口径：铝合金产品销量281.1万吨(H1,-3.3%)、深加工44.4万吨(+23.2%)；产量年报才披露</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -5445,7 +5421,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>云南神火水电铝摆脱 2023 年限电影响后负荷提升、新疆基地稳产</t>
+          <t>2026中报(7/27)仅定性'满产满销,时间过半任务过半'（产能170万吨/年），无吨数；另披露铝箔6.38万吨(+20%)</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -5548,19 +5524,15 @@
         <f>IF(AND(ISNUMBER(R15),ISNUMBER(M15),M15&lt;&gt;0),(R15-M15)/M15,"-")</f>
         <v/>
       </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T15" s="2" t="n">
+        <v>81</v>
       </c>
       <c r="U15" s="5">
         <f>IF(AND(ISNUMBER(T15),ISNUMBER(N15),N15&lt;&gt;0),(T15-N15)/N15,"-")</f>
         <v/>
       </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V15" s="2" t="n">
+        <v>81</v>
       </c>
       <c r="W15" s="5">
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
@@ -5568,7 +5540,7 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>2024 +22.45%：2023 年云南能效管理限产低基数+2024 争取用电负荷快速复产</t>
+          <t>2026中报(8/27)：H1铝产品(铝商品口径,含合金及加工)162万吨(约+1%)；全年目标319万吨完成50.8%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -5578,7 +5550,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>口径警示：2025 年报改'铝商品'口径（含合金及加工），不再单列原铝；H1：23年97.40/24年135.07/25年161.32（铝产品）｜2025年报：电解铝毛利率18.16%(+4.92pct)；对中铝集团关联销售占32%</t>
+          <t>口径警示：2025 年报改'铝商品'口径（含合金及加工），不再单列原铝；H1：23年97.40/24年135.07/25年161.32（铝产品）｜2025年报：电解铝毛利率18.16%(+4.92pct)；对中铝集团关联销售占32%；2026中报H1铝商品累计162万吨，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -5671,19 +5643,15 @@
         <f>IF(AND(ISNUMBER(R16),ISNUMBER(M16),M16&lt;&gt;0),(R16-M16)/M16,"-")</f>
         <v/>
       </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T16" s="2" t="n">
+        <v>33.025</v>
       </c>
       <c r="U16" s="5">
         <f>IF(AND(ISNUMBER(T16),ISNUMBER(N16),N16&lt;&gt;0),(T16-N16)/N16,"-")</f>
         <v/>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V16" s="2" t="n">
+        <v>33.025</v>
       </c>
       <c r="W16" s="5">
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
@@ -5691,7 +5659,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>产能稳定；140 万吨绿色低碳能效提升项目剩余部分 2026H1 投产，产能将升至 140 万吨/年</t>
+          <t>2026中报(8/18)：H1电解铝66.05万吨(+12.8%,140万吨技改项目爬产,下半年还有增量)</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -5701,7 +5669,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>H1：23年57.80/24年58.54/25年58.54；季报不披露产量</t>
+          <t>H1：23年57.80/24年58.54/25年58.54；季报不披露产量；2026中报H1累计66.05万吨，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6036,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>季报不披露产量吨数（已核验2026Q1季报全文，仅定性表述）</t>
+          <t>季报不披露产量吨数（2026Q1/Q2季报均已核验,仅财务口径；26Q2核心净利+42%）；产能锚点1.08Mtpa</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -6078,7 +6046,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>公司季报无产量披露；产能锚点：Mukah 12万吨+Samalaju三期96万吨=108万吨/年（2021年满产）；如需可按满产~27万吨/季自行估算（推算值非披露）；26Q2财报预计2026年8月下旬</t>
+          <t>公司季报无产量披露；产能锚点：Mukah 12万吨+Samalaju三期96万吨=108万吨/年（2021年满产）；如需可按满产~27万吨/季自行估算（推算值非披露）；2026Q2 季报已披露（Bursa 公告 8/27，报道 8/28），未披露产量吨数（仅财务口径，已二次核验）</t>
         </is>
       </c>
     </row>
@@ -6160,10 +6128,8 @@
         <f>IF(AND(ISNUMBER(T20),ISNUMBER(N20),N20&lt;&gt;0),(T20-N20)/N20,"-")</f>
         <v/>
       </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V20" s="2" t="n">
+        <v>13.06</v>
       </c>
       <c r="W20" s="5">
         <f>IF(AND(ISNUMBER(V20),ISNUMBER(O20),O20&lt;&gt;0),(V20-O20)/O20,"-")</f>
@@ -6171,7 +6137,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>25Q4-26Q1大跌主因Grundartangi 2号线2025年10月底设备故障（已获保险赔付），2026年4月启动重启；Mt.Holly 26Q2末前重启5万吨</t>
+          <t>26Q2 出货量 130,632 吨=13.06 万吨（环比+6%：Mt. Holly 最后 90 槽重启完成+Grundartangi 2 号线恢复近满产）。源：Century Q2 2026 业绩（8-K ex99.1）</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -6256,10 +6222,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O21" s="2" t="n">
+        <v>40.29</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
@@ -6289,16 +6253,18 @@
         <f>IF(AND(ISNUMBER(T21),ISNUMBER(N21),N21&lt;&gt;0),(T21-N21)/N21,"-")</f>
         <v/>
       </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V21" s="2" t="n">
+        <v>15.55</v>
       </c>
       <c r="W21" s="5">
         <f>IF(AND(ISNUMBER(V21),ISNUMBER(O21),O21&lt;&gt;0),(V21-O21)/O21,"-")</f>
         <v/>
       </c>
-      <c r="X21" s="3" t="n"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>26Q2 净成品铝产量 155,469 吨=15.55 万吨（同比-61%：地区紧张局势对 1/2/3 号线控制性停产）；销量 280,799 吨（-32%）。源：Alba Q2/H1 2026 业绩（2026-08-04）</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="n"/>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -6401,25 +6367,25 @@
         <f>IF(AND(ISNUMBER(R22),ISNUMBER(M22),M22&lt;&gt;0),(R22-M22)/M22,"-")</f>
         <v/>
       </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T22" s="2" t="n">
+        <v>24.9</v>
       </c>
       <c r="U22" s="5">
         <f>IF(AND(ISNUMBER(T22),ISNUMBER(N22),N22&lt;&gt;0),(T22-N22)/N22,"-")</f>
         <v/>
       </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V22" s="2" t="n">
+        <v>24.2</v>
       </c>
       <c r="W22" s="5">
         <f>IF(AND(ISNUMBER(V22),ISNUMBER(O22),O22&lt;&gt;0),(V22-O22)/O22,"-")</f>
         <v/>
       </c>
-      <c r="X22" s="3" t="n"/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>26Q2 原铝 242,000 吨=24.2 万吨（环比微降）；铝板块收入 +49% 至 $1.01bn（均价+51%）。26Q1=24.9 为二手源（vision2030，待核）。源：Ma'aden Q2 2026（Tadawul，8 月上旬）/AlCircle</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="n"/>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -6550,7 +6516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6677,6 +6643,40 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>铝 26Q2 欠账补录：Century 13.06 / Alba 15.55（-61% 停产事件）/ Ma'aden 24.2 万吨；Hindalco 33.5（出货量口径）；RUSAL H1=201.0（半年口径）；Ma'aden 铝土矿/氧化铝未找到</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Century 8-K；Alba 官网 8/4；Ma'aden Tadawul/AlCircle；Hindalco 官网 8/7；RUSAL HKEX 8/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>铝 26Q2 回填：NALCO三板块(矿182.9/氧57.7/铝11.6,Q1FY27官方演示稿)；中铝氧333+原铝201（中报H1−Q1推算）；云铝H1=65/162；天山H1=126.23/66.05；宏桥/神火=未披露(中报仅销量/定性)；Press Metal核验26Q2季报仍无产量(保持'-')</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NALCO官网新闻稿8/1+演示稿；中铝/云铝/天山/神火中报(巨潮)；宏桥港交所中报8/21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/铝.xlsx
+++ b/excel/铝.xlsx
@@ -1888,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1914,8 +1914,8 @@
     <col width="8.5" customWidth="1" min="21" max="21"/>
     <col width="8.5" customWidth="1" min="22" max="22"/>
     <col width="8.5" customWidth="1" min="23" max="23"/>
-    <col width="46" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="8.5" customWidth="1" min="24" max="24"/>
+    <col width="8.5" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
@@ -2037,15 +2037,25 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>26Q3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>26Q3同比</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>变化原因</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>FY2026指引</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -2130,17 +2140,19 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="X2" s="4" t="n"/>
+      <c r="Y2" s="5" t="n"/>
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>Kwinana 关停/San Ciprián 减产致连年下滑；2026Q2 环比-6%：Pinjarra 运行不稳+飓风 Narelle 气供中断</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>950–960（自 970–990 下调）</t>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>SEC 8-K 合并口径；产量不拆第三方/自用（仅发运量有拆分）；2026Q2 宣布收购 South32 铝资产</t>
         </is>
@@ -2225,17 +2237,19 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="X3" s="4" t="n"/>
+      <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>2026 起 QAL 改按 100% 口径并表+炼厂运行改善（Q1 +6%/Q2 +10%）；2024Q2 -10% 系昆士兰天然气管道破裂冲击 Gladstone</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>760–800</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>权益口径；2026Q1 起 QAL 100% 并表（此前 80% 权益）；2023 年多季及 2025 年各季为官方 0.1Mt 精度值或推算值</t>
         </is>
@@ -2320,17 +2334,19 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="X4" s="4" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>2025Q4 达 1,616kt 超铭牌运行，2026 维持高位（收得率改善+设备稳定）</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>无（non-guidance policy）</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Alunorte 100% 口径（Hydro 持股 62%，披露仍为 100% 产量）</t>
         </is>
@@ -2439,17 +2455,19 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="X5" s="2" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>2026H1（8/19 港交所中报）：氧化铝产量 365.8 万吨（+7.6%，增量主要来自 2025-07 收购的印度 Pioneer 氧化铝厂 26% 权益）——半年口径，季度不拆；26Q1 未披露，Q1=Q2=H1/2=182.9 拟合。源：RUSAL 2026 中期业绩（HKEX 2026-08-19）</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>2022 年起停发季报，仅半年度/年度（H1：24年299.5/25年340.0）；同比分析须注意口径跳变；2026H1=365.8（HKEX 中报原文 Alumina 3,658kt），Q1 未披露两季平分拟合</t>
         </is>
@@ -2540,17 +2558,19 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="X6" s="4" t="n"/>
+      <c r="Y6" s="5" t="n"/>
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>FY26 持平（铝土矿供应改善被 3 月季气旋 Narelle 及第三方天然气中断抵消）；2026-07 宣布随铝资产出售给美铝</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>FY27（2026.7–2027.6）：390</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>86%权益、可销售产量；财年止6月；2023Q1-Q2 分资产值未找到；2023Q3-2025Q1 多季为推算值；财年合计 FY24 377.7 / FY25 372.7 / FY26 372.2</t>
         </is>
@@ -2657,17 +2677,19 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="X7" s="4" t="n"/>
+      <c r="Y7" s="5" t="n"/>
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>FY26 141.1 万吨（超指引 136）</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>FY27：136</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="AB7" s="3" t="inlineStr">
         <is>
           <t>36%非运营权益；早期季度未找到；财年合计 FY24 128.6 / FY25 134.0 / FY26 141.1</t>
         </is>
@@ -2752,17 +2774,21 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="X8" s="4" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="Y8" s="5" t="n"/>
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>Lanjigarh 扩产 2→3.5→5 Mtpa 逐段投产（2025Q4 Train II 投产、2026Q1 同比+104%）</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>FY27：400–410</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>财年止3月（Q1FY=自然季Q2）；2026Q2≈82.8 为推算值（媒体披露+41% 同比）；2026-05 拆分后归属 VAML</t>
         </is>
@@ -2849,17 +2875,19 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="X9" s="2" t="n"/>
+      <c r="Y9" s="5" t="n"/>
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>Q1FY27（=26Q2）业绩 8/7 已发：仅披露铝上游出货量 335kt，氧化铝产量未在新闻稿披露 → 未披露。源：Hindalco Q1FY27 业绩新闻稿（2026-08-07）</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>无量化指引（Aditya 85万吨绿地氧化铝厂目标 FY28）</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>'Hydrate as Alumina'总量（含 Utkal）；财年止3月；个别季度前后版本有±1-2kt 重列；2026Q2 未披露（预计 8 月中）</t>
         </is>
@@ -2974,17 +3002,19 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="X10" s="2" t="n"/>
+      <c r="Y10" s="5" t="n"/>
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>Q1FY27(=26Q2)：煅烧氧化铝57.7万吨（创Q1纪录；水合物57.8万吨）；官方新闻稿8/1+演示稿</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>无（氧化铝厂第5系列 +1Mt 扩产推进中）</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>财年止3月；FY25≈204.7 为按 FY26 同比反推的推算值；FY24 未找到；季度绝对量不披露；FY26 值见变化原因</t>
         </is>
@@ -3089,17 +3119,19 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="5" t="n"/>
+      <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/27)：H1冶金级氧化铝738万吨(-14.19%)−26Q1 405=333（推算）；另精细氧化铝H1 234万吨(+12.5%)</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>未找到（2025 目标 1,681，实际 1,735）</t>
         </is>
       </c>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="AB11" s="3" t="inlineStr">
         <is>
           <t>季报仅 Q1 当季/Q3 累计披露产量（25H1 860、2025 前三季 1,304）；另披露精细氧化铝（2025 年 451）｜2025年报：氧化铝板块毛利率约17.5%(-8.86pct，氧化铝均价-21%)；归母净利126.74亿历史最优；2026/1拟联合力拓收购巴西铝业68.6%股权</t>
         </is>
@@ -3214,17 +3246,19 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
-      <c r="X12" s="3" t="inlineStr">
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="5" t="n"/>
+      <c r="Z12" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/21港交所)仅销量口径：氧化铝销量691.7万吨(H1,+8.6%)；产量年报才披露</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
+      <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>无（氧化铝产能 2,100 万吨含印尼 200 万吨）</t>
         </is>
       </c>
-      <c r="Z12" s="3" t="inlineStr">
+      <c r="AB12" s="3" t="inlineStr">
         <is>
           <t>2024 为 2025 年报同口径可比数；2023 及以前港股年报仅披露销量；港股无季报；宏桥控股(002379.SZ)与中国宏桥(1378.HK)为同一资产，不重复计列</t>
         </is>
@@ -3333,17 +3367,19 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
-      <c r="X13" s="3" t="inlineStr">
+      <c r="X13" s="2" t="n"/>
+      <c r="Y13" s="5" t="n"/>
+      <c r="Z13" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/27)：H1氧化铝产量65万吨(-3%)；Q1未单独披露,记H1累计</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
+      <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>2026：约130</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
+      <c r="AB13" s="3" t="inlineStr">
         <is>
           <t>半年报披露 H1（23H1 73.32 / 24H1 72.30 / 25H1 66.97）；季报不披露产量；2026中报H1累计65万吨，Q1未披露，两季平分拟合</t>
         </is>
@@ -3452,17 +3488,19 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="X14" s="2" t="n"/>
+      <c r="Y14" s="5" t="n"/>
+      <c r="Z14" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/18)：H1氧化铝产量126.23万吨(+5%)</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>2026：260</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
+      <c r="AB14" s="3" t="inlineStr">
         <is>
           <t>半年报披露 H1（23H1 102.33 / 24H1 109.30 / 25H1 119.99）；季报不披露产量｜2025年报：氧化铝毛利率9.7%(2025H1尚有14.6%，下半年走弱)；2026中报H1累计126.23万吨，Q1未披露，两季平分拟合</t>
         </is>
@@ -3577,17 +3615,19 @@
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
         <v/>
       </c>
-      <c r="X15" s="3" t="inlineStr">
+      <c r="X15" s="2" t="n"/>
+      <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>2023 产量翻倍系滨州二期 400kt 投产+超产（利用率 128.8%）</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>2,000kt 氧化铝焙烧线 2025-11 试产</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="AB15" s="3" t="inlineStr">
         <is>
           <t>招股书披露（千吨÷10）；2025 年报未披露绝对产量（仅收入）；2025-11-24 港股上市，无季报</t>
         </is>
@@ -3706,13 +3746,15 @@
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
-      <c r="X16" s="3" t="inlineStr">
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="5" t="n"/>
+      <c r="Z16" s="3" t="inlineStr">
         <is>
           <t>Ma'aden Q2 2026 已披露，但 Ras Al Khair 氧化铝分季产量未见公开披露（二手源 vision2030 称某季 47.8 万吨，口径待核）→ 未找到。源：Ma'aden Q2 2026 / AlCircle</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="n"/>
-      <c r="Z16" s="3" t="inlineStr">
+      <c r="AA16" s="3" t="n"/>
+      <c r="AB16" s="3" t="inlineStr">
         <is>
           <t>季报（Tadawul）≈季后4-5周；2026-08-18新增骨架行，数据待回填</t>
         </is>
@@ -3814,17 +3856,19 @@
         <f>IF(AND(ISNUMBER(V17),ISNUMBER(O17),O17&lt;&gt;0),(V17-O17)/O17,"-")</f>
         <v/>
       </c>
-      <c r="X17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z17" s="9" t="inlineStr">
+      <c r="X17" s="7" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB17" s="9" t="inlineStr">
         <is>
           <t>有数据列直接求和；注意口径混杂（权益/100%合并/湿吨/半年度/财年值），仅作量级参考。俄铝为年度值（计入总计列）；NALCO 为财年值（财年止3月）；South32 财年止6月；印度三家财年止3月</t>
         </is>
@@ -3841,7 +3885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3867,8 +3911,8 @@
     <col width="8.5" customWidth="1" min="21" max="21"/>
     <col width="8.5" customWidth="1" min="22" max="22"/>
     <col width="8.5" customWidth="1" min="23" max="23"/>
-    <col width="46" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="8.5" customWidth="1" min="24" max="24"/>
+    <col width="8.5" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
@@ -3990,15 +4034,25 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>26Q3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>26Q3同比</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>变化原因</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>FY2026指引</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -4083,17 +4137,19 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="X2" s="4" t="n"/>
+      <c r="Y2" s="5" t="n"/>
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>San Ciprián（2026-04 重启完成）/Alumar/Lista/Portland 重启推动连增，2026Q2 636kt 环比+5%</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>240–260（维持不变）</t>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>SEC 8-K 合并报表口径（非权益）</t>
         </is>
@@ -4178,17 +4234,19 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="X3" s="4" t="n"/>
+      <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>2025 +3% 至指引上限（NZAS 爬坡完成）；2026H1 基本持平</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>325–345</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>权益口径；2023Q1/Q2/Q4 及 2025 年各季为官方 0.1Mt 精度值或推算值</t>
         </is>
@@ -4273,17 +4331,19 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="X4" s="4" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>2026Q2 -3%：Qatalum 自 2026-03 起因供气受限维持约60%开工的完整季度影响，部分被挪威爬坡抵消</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>无（Slovalco 75kt 产能 2026H2 重启）</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>挪威本土厂+Albras+Neuss 100% 产量 + Qatalum（持股50%）按比例计入</t>
         </is>
@@ -4392,17 +4452,19 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="X5" s="2" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>2026H1（8/19 港交所中报）：原铝产量 2.010 百万吨（+4.5%）——半年口径，季度不拆。源：RUSAL 2026 中期业绩（HKEX 2026-08-19）</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>2022 年起停发季报，仅半年度/年度（H1：23年191.3推算/24年195.7/25年192.4）；注意 2025 销量大增系去库存，与产量走势背离，勿混用；2026中报(8/19港交所)H1原铝201.0万吨(+4.5%)，Q1未披露，两季平分拟合</t>
         </is>
@@ -4503,17 +4565,19 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="X6" s="4" t="n"/>
+      <c r="Y6" s="5" t="n"/>
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>持续测试最大技术产能，FY26 受南非限电（load-shedding）影响</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>FY27：72</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>2023Q1-2024Q1 分季度值未找到（季度均值≈180kt）；2024Q2-2025Q1、2025Q3-Q4 为推算值；财年合计 FY24 72.0 / FY25 71.8 / FY26 71.7</t>
         </is>
@@ -4622,17 +4686,19 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="X7" s="4" t="n"/>
+      <c r="Y7" s="5" t="n"/>
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>2026-03-15 电力协议到期未续约，转入维护保养（care &amp; maintenance），2026Q2 产量为 0</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>停产，无指引</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="AB7" s="3" t="inlineStr">
         <is>
           <t>2024Q3-2025Q1 未找到（约85-91kt/季）；2025Q3-Q4 为推算值（两季合计183kt）；财年合计 FY24 31.4 / FY25 35.5 / FY26 24.8</t>
         </is>
@@ -4745,17 +4811,19 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="X8" s="4" t="n"/>
+      <c r="Y8" s="5" t="n"/>
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>FY25 +33%（三条电解槽线复产爬坡），FY26 +4%（爬坡完成）</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>FY27：14</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>40%非运营权益；多数季度未找到；财年合计 FY24 10.4 / FY25 13.8 / FY26 14.4</t>
         </is>
@@ -4840,17 +4908,21 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="X9" s="4" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="Y9" s="5" t="n"/>
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>基本满产稳定；2026Q2 创历史最高季度（BALCO 新建 525kA 电解槽系列投产贡献）</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>FY27：260–270</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>财年止3月（Q1FY=自然季Q2）；个别季度后续公告有≤1kt 重列；2026-05 拆分后归属 VAML</t>
         </is>
@@ -4935,17 +5007,19 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="X10" s="2" t="n"/>
+      <c r="Y10" s="5" t="n"/>
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>Q1FY27（=26Q2）铝上游出货量 335kt=33.5 万吨（同比+3%，出货量口径）；上游 EBITDA 创纪录 ₹7,390  crore（+81%）；Aditya 二期 FY28 投产。源：Hindalco Q1FY27 业绩新闻稿（2026-08-07）</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>无量化指引（Aditya 电解铝扩产在建）</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>财年止3月；2026Q2 未披露（预计 8 月中）</t>
         </is>
@@ -5058,17 +5132,19 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="5" t="n"/>
+      <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>Q1FY27(=26Q2)：电解铝11.6万吨（上年同季11.5）；官方演示稿</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>无（电解铝厂与自备电厂棕地扩建推进中）</t>
         </is>
       </c>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="AB11" s="3" t="inlineStr">
         <is>
           <t>财年止3月：FY24=46.3 列于24总计；FY25≈46.0 为按 FY26 同比反推的推算值；季度绝对量不披露；FY26 值见变化原因</t>
         </is>
@@ -5173,17 +5249,19 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
-      <c r="X12" s="3" t="inlineStr">
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="5" t="n"/>
+      <c r="Z12" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/27)：H1原铝(含合金)402万吨(+1.26%)−26Q1 201=201（推算）</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
+      <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>未找到（2025 目标 780，实际 808）</t>
         </is>
       </c>
-      <c r="Z12" s="3" t="inlineStr">
+      <c r="AB12" s="3" t="inlineStr">
         <is>
           <t>季报仅 Q1 当季/Q3 累计披露产量（25H1 397、2025 前三季 600）｜2025年报：原铝板块毛利率18.88%(+8.57pct，铝价涨+氧化铝/煤成本降)；808万吨为含合金口径</t>
         </is>
@@ -5296,17 +5374,19 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
-      <c r="X13" s="3" t="inlineStr">
+      <c r="X13" s="2" t="n"/>
+      <c r="Y13" s="5" t="n"/>
+      <c r="Z13" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/21港交所)仅销量口径：铝合金产品销量281.1万吨(H1,-3.3%)、深加工44.4万吨(+23.2%)；产量年报才披露</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
+      <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>无量化指引</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
+      <c r="AB13" s="3" t="inlineStr">
         <is>
           <t>2024 为推算值（2025 年报同口径可比数 653.52）；港股无季报（H1：23年305.9/24年322.1）；宏桥控股(002379.SZ)同一资产不重复计列</t>
         </is>
@@ -5419,17 +5499,19 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="X14" s="2" t="n"/>
+      <c r="Y14" s="5" t="n"/>
+      <c r="Z14" s="3" t="inlineStr">
         <is>
           <t>2026中报(7/27)仅定性'满产满销,时间过半任务过半'（产能170万吨/年），无吨数；另披露铝箔6.38万吨(+20%)</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>2026：铝产品 170（内部管理控制指标，非承诺）</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
+      <c r="AB14" s="3" t="inlineStr">
         <is>
           <t>口径警示：2025 年报改为'有色金属冶炼和压延加工'（含加工产品，重述2024=189.15），与此前'铝产品'口径不可直接比较；产量仅年报披露；无自产氧化铝（外购）｜2025年报：电解铝毛利率30.06%(+4.95pct)、吨毛利约5100元；煤炭资产减值12.56亿(Q4集中计提)；2026计划铝产品170万吨</t>
         </is>
@@ -5538,17 +5620,19 @@
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
         <v/>
       </c>
-      <c r="X15" s="3" t="inlineStr">
+      <c r="X15" s="2" t="n"/>
+      <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/27)：H1铝产品(铝商品口径,含合金及加工)162万吨(约+1%)；全年目标319万吨完成50.8%</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>2026：铝商品约319</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="AB15" s="3" t="inlineStr">
         <is>
           <t>口径警示：2025 年报改'铝商品'口径（含合金及加工），不再单列原铝；H1：23年97.40/24年135.07/25年161.32（铝产品）｜2025年报：电解铝毛利率18.16%(+4.92pct)；对中铝集团关联销售占32%；2026中报H1铝商品累计162万吨，Q1未披露，两季平分拟合</t>
         </is>
@@ -5657,17 +5741,19 @@
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
-      <c r="X16" s="3" t="inlineStr">
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="5" t="n"/>
+      <c r="Z16" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/18)：H1电解铝66.05万吨(+12.8%,140万吨技改项目爬产,下半年还有增量)</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
+      <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>2026：135</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
+      <c r="AB16" s="3" t="inlineStr">
         <is>
           <t>H1：23年57.80/24年58.54/25年58.54；季报不披露产量；2026中报H1累计66.05万吨，Q1未披露，两季平分拟合</t>
         </is>
@@ -5782,17 +5868,19 @@
         <f>IF(AND(ISNUMBER(V17),ISNUMBER(O17),O17&lt;&gt;0),(V17-O17)/O17,"-")</f>
         <v/>
       </c>
-      <c r="X17" s="3" t="inlineStr">
+      <c r="X17" s="2" t="n"/>
+      <c r="Y17" s="5" t="n"/>
+      <c r="Z17" s="3" t="inlineStr">
         <is>
           <t>产能利用率 94-96%，稳定在 75 万吨级</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
+      <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>铝锭产量预计同比 +5%~10%（液铝转铝锭结构调整）</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="inlineStr">
+      <c r="AB17" s="3" t="inlineStr">
         <is>
           <t>招股书披露（千吨÷10）；2025 年报未披露绝对产量；2025-11-24 港股上市，无季报</t>
         </is>
@@ -5905,17 +5993,19 @@
         <f>IF(AND(ISNUMBER(V18),ISNUMBER(O18),O18&lt;&gt;0),(V18-O18)/O18,"-")</f>
         <v/>
       </c>
-      <c r="X18" s="3" t="inlineStr">
+      <c r="X18" s="2" t="n"/>
+      <c r="Y18" s="5" t="n"/>
+      <c r="Z18" s="3" t="inlineStr">
         <is>
           <t>安哥拉年产 12 万吨电解铝项目 2026 年 1 月正式投产试运行</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
+      <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>无明确目标（'快速提升产能利用率与产量规模'）</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="inlineStr">
+      <c r="AB18" s="3" t="inlineStr">
         <is>
           <t>2023-2025 为建设期（产量 0）；2026Q1 未披露铝产量</t>
         </is>
@@ -6034,17 +6124,19 @@
         <f>IF(AND(ISNUMBER(V19),ISNUMBER(O19),O19&lt;&gt;0),(V19-O19)/O19,"-")</f>
         <v/>
       </c>
-      <c r="X19" s="3" t="inlineStr">
+      <c r="X19" s="2" t="n"/>
+      <c r="Y19" s="5" t="n"/>
+      <c r="Z19" s="3" t="inlineStr">
         <is>
           <t>季报不披露产量吨数（2026Q1/Q2季报均已核验,仅财务口径；26Q2核心净利+42%）；产能锚点1.08Mtpa</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
+      <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>待补</t>
         </is>
       </c>
-      <c r="Z19" s="3" t="inlineStr">
+      <c r="AB19" s="3" t="inlineStr">
         <is>
           <t>公司季报无产量披露；产能锚点：Mukah 12万吨+Samalaju三期96万吨=108万吨/年（2021年满产）；如需可按满产~27万吨/季自行估算（推算值非披露）；2026Q2 季报已披露（Bursa 公告 8/27，报道 8/28），未披露产量吨数（仅财务口径，已二次核验）</t>
         </is>
@@ -6135,17 +6227,19 @@
         <f>IF(AND(ISNUMBER(V20),ISNUMBER(O20),O20&lt;&gt;0),(V20-O20)/O20,"-")</f>
         <v/>
       </c>
-      <c r="X20" s="3" t="inlineStr">
+      <c r="X20" s="2" t="n"/>
+      <c r="Y20" s="5" t="n"/>
+      <c r="Z20" s="3" t="inlineStr">
         <is>
           <t>26Q2 出货量 130,632 吨=13.06 万吨（环比+6%：Mt. Holly 最后 90 槽重启完成+Grundartangi 2 号线恢复近满产）。源：Century Q2 2026 业绩（8-K ex99.1）</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
+      <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>无吨数指引（26Q2 Adj.EBITDA指引3.15-3.35亿美元）</t>
         </is>
       </c>
-      <c r="Z20" s="3" t="inlineStr">
+      <c r="AB20" s="3" t="inlineStr">
         <is>
           <t>出货量(shipments)口径非产量·100%口径（美国Sebree/Mt.Holly+冰岛Grundartangi）；26Q2财报预计2026年8月上旬（近三年均8/7-8/9发布）</t>
         </is>
@@ -6260,13 +6354,15 @@
         <f>IF(AND(ISNUMBER(V21),ISNUMBER(O21),O21&lt;&gt;0),(V21-O21)/O21,"-")</f>
         <v/>
       </c>
-      <c r="X21" s="3" t="inlineStr">
+      <c r="X21" s="2" t="n"/>
+      <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="3" t="inlineStr">
         <is>
           <t>26Q2 净成品铝产量 155,469 吨=15.55 万吨（同比-61%：地区紧张局势对 1/2/3 号线控制性停产）；销量 280,799 吨（-32%）。源：Alba Q2/H1 2026 业绩（2026-08-04）</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="n"/>
-      <c r="Z21" s="3" t="inlineStr">
+      <c r="AA21" s="3" t="n"/>
+      <c r="AB21" s="3" t="inlineStr">
         <is>
           <t>大型电解铝厂；季报≈季后4-6周；2026-08-18新增骨架行，数据待回填</t>
         </is>
@@ -6381,13 +6477,15 @@
         <f>IF(AND(ISNUMBER(V22),ISNUMBER(O22),O22&lt;&gt;0),(V22-O22)/O22,"-")</f>
         <v/>
       </c>
-      <c r="X22" s="3" t="inlineStr">
+      <c r="X22" s="2" t="n"/>
+      <c r="Y22" s="5" t="n"/>
+      <c r="Z22" s="3" t="inlineStr">
         <is>
           <t>26Q2 原铝 242,000 吨=24.2 万吨（环比微降）；铝板块收入 +49% 至 $1.01bn（均价+51%）。26Q1=24.9 为二手源（vision2030，待核）。源：Ma'aden Q2 2026（Tadawul，8 月上旬）/AlCircle</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="n"/>
-      <c r="Z22" s="3" t="inlineStr">
+      <c r="AA22" s="3" t="n"/>
+      <c r="AB22" s="3" t="inlineStr">
         <is>
           <t>季报（Tadawul）≈季后4-5周；2026-08-18新增骨架行，数据待回填</t>
         </is>
@@ -6489,17 +6587,19 @@
         <f>IF(AND(ISNUMBER(V23),ISNUMBER(O23),O23&lt;&gt;0),(V23-O23)/O23,"-")</f>
         <v/>
       </c>
-      <c r="X23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z23" s="9" t="inlineStr">
+      <c r="X23" s="7" t="n"/>
+      <c r="Y23" s="8" t="n"/>
+      <c r="Z23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB23" s="9" t="inlineStr">
         <is>
           <t>有数据列直接求和；注意口径混杂（权益/100%合并/湿吨/半年度/财年值），仅作量级参考。俄铝为年度值（计入总计列）；NALCO 为财年值（财年止3月）；South32 财年止6月；印度三家财年止3月</t>
         </is>
@@ -6516,7 +6616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6677,6 +6777,23 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>开 26Q3 列。Vedanta Q2FY27(7-9月)入库：氧化铝(Lanjigarh) 89.5万吨(+37% YoY，季度纪录，扩产爬坡)；电解铝 64.9万吨(+5%，季度纪录；Jharsuguda 47.0万吨+BALCO 17.8万吨+19%)。</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Vedanta Q2FY27 Production Release 2026-10-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/铝.xlsx
+++ b/excel/铝.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -492,8 +492,8 @@
     <col width="8.5" customWidth="1" min="21" max="21"/>
     <col width="8.5" customWidth="1" min="22" max="22"/>
     <col width="8.5" customWidth="1" min="23" max="23"/>
-    <col width="46" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="8.5" customWidth="1" min="24" max="24"/>
+    <col width="8.5" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
@@ -615,15 +615,25 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>26Q3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>26Q3同比</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>变化原因</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>FY2026指引</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -708,17 +718,24 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>2026Q2 环比-9%：西澳飓风 Narelle 扰动（官方未单独归因）；中长期受西澳矿山品位与 Myara 等矿权过渡影响</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="X2" s="4" t="n">
+        <v>930</v>
+      </c>
+      <c r="Y2" s="5">
+        <f>IF(AND(ISNUMBER(X2),ISNUMBER(P2),P2&lt;&gt;0),(X2-P2)/P2,"-")</f>
+        <v/>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>26Q3铝土矿930万吨（9.3mdmt），同比持平；SEC 8-K EX-99.1</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>不按年度给铝土矿产量指引</t>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>SEC 8-K EX-99.1 合并报表口径（非权益）；2026Q2 宣布收购 South32 铝资产（Worsley 等），后续留意并表时点</t>
         </is>
@@ -803,17 +820,24 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>2026Q1 同比-11%（Weipa 强降雨+3月气旋 Narelle 冲击 Weipa/Gove），Q2 环比+14% 恢复；2024-2025 靠 Amrun 超铭牌运行连创纪录</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="X3" s="4" t="n">
+        <v>1574.5</v>
+      </c>
+      <c r="Y3" s="5">
+        <f>IF(AND(ISNUMBER(X3),ISNUMBER(P3),P3&lt;&gt;0),(X3-P3)/P3,"-")</f>
+        <v/>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>26Q3铝土矿1,574.5万湿吨（15.7448Mt），同比-4%/环比+4%；Rio Q3官方production XLSX</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>5,800–6,100（权益）</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>权益口径、湿吨；23Q4 为全年减前三季推算值</t>
         </is>
@@ -898,17 +922,24 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>2026Q1 +7% 系矿石品位改善；2024Q3 单季骤降（2,258kt）公司未明确归因</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="X4" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="Y4" s="5">
+        <f>IF(AND(ISNUMBER(X4),ISNUMBER(P4),P4&lt;&gt;0),(X4-P4)/P4,"-")</f>
+        <v/>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>26Q3 Paragominas铝土矿241.0万吨（湿基），同比-5%/环比-9%；Hydro Q3 Report</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>无（公司执行 non-guidance policy）</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Paragominas 湿基产量；公司季报原始披露</t>
         </is>
@@ -1017,17 +1048,26 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y5" s="5">
+        <f>IF(AND(ISNUMBER(X5),ISNUMBER(P5),P5&lt;&gt;0),(X5-P5)/P5,"-")</f>
+        <v/>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>2026H1（8/19 港交所中报）：铝土矿产量 1,090.5 万湿吨（+12.8%）——半年口径，季度不拆；26Q1 未披露，Q1=Q2=H1/2=545.25 拟合。源：RUSAL 2026 中期业绩（HKEX 2026-08-19）</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>2022 年起停发季报，仅半年度/年度披露（H1：23年675.4推算/24年794.0/25年966.8）；湿吨；2026H1=1,090.5（湿吨，HKEX 中报原文 Bauxite (wet) 10,905kt），Q1 未披露两季平分拟合</t>
         </is>
@@ -1146,17 +1186,26 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y6" s="5">
+        <f>IF(AND(ISNUMBER(X6),ISNUMBER(P6),P6&lt;&gt;0),(X6-P6)/P6,"-")</f>
+        <v/>
       </c>
       <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>Worsley 配套 Boddington 矿自供、巴西 MRN 为 33% 非运营权益，季报产量表不含铝土矿</t>
         </is>
@@ -1269,17 +1318,26 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y7" s="5">
+        <f>IF(AND(ISNUMBER(X7),ISNUMBER(P7),P7&lt;&gt;0),(X7-P7)/P7,"-")</f>
+        <v/>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>Q1FY27(=26Q2)：铝土矿产量182.9万吨（官方演示稿Physical Performance；新闻稿开采口径195.2万吨创Q1纪录）</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>无（Pottangi 铝土矿计划 2026 年 6 月启动投产）</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="AB7" s="3" t="inlineStr">
         <is>
           <t>财年止3月：FY24=752.7（运输口径，开采量未找到）列于24总计，FY25=764.8（开采，创纪录）列于25总计；季度绝对量不披露；FY26 值见变化原因</t>
         </is>
@@ -1396,17 +1454,26 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y8" s="5">
+        <f>IF(AND(ISNUMBER(X8),ISNUMBER(P8),P8&lt;&gt;0),(X8-P8)/P8,"-")</f>
+        <v/>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/27)未披露铝土矿产量（中铝半年报惯例不披露,年报才有）</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>仅 2023 年报披露铝土矿产量 3,042 万吨；2024/2025 年报数据未核到，待补</t>
         </is>
@@ -1523,17 +1590,26 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>几内亚铝土矿 2025 年进入生产开采并发运回国</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y9" s="5">
+        <f>IF(AND(ISNUMBER(X9),ISNUMBER(P9),P9&lt;&gt;0),(X9-P9)/P9,"-")</f>
+        <v/>
       </c>
       <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>几内亚铝土矿2025年进入生产开采并发运回国；2026中报(8/25)复核无铝土矿开采量绝对值（仅定性"产能及运力仍在爬升中"），26Q2保持空缺(2026-10-14复核)</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>2025 年报表述为'采矿超100万吨'，100 为下限、采矿口径而非发运量；2023-2024 尚未规模开采｜2025年报：自产铝锭毛利率30.46%、氧化铝9.7%(价跌+成本上行)；几内亚全链条运营元年；2026计划原铝135万吨</t>
         </is>
@@ -1624,17 +1700,26 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10月末)</t>
+        </is>
+      </c>
+      <c r="Y10" s="5">
+        <f>IF(AND(ISNUMBER(X10),ISNUMBER(P10),P10&lt;&gt;0),(X10-P10)/P10,"-")</f>
+        <v/>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>26Q2发运180万吨(+7%,Q2纪录)；Q1雨季基本停产，强季节性</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>2026发运指引660-710万湿吨</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>发运量(shipments)口径·湿公吨WMT（产量仅零星披露且≈发运量）；26Q2来自2026-07-07运营更新，正式季报未出</t>
         </is>
@@ -1753,13 +1838,22 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y11" s="5">
+        <f>IF(AND(ISNUMBER(X11),ISNUMBER(P11),P11&lt;&gt;0),(X11-P11)/P11,"-")</f>
+        <v/>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>Ma'aden Q2 2026 已披露（铝板块收入+49%），但铝土矿分季产量未见公开披露 → 未找到。源：Ma'aden Q2 2026 / AlCircle 2026-08-11</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="n"/>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="AA11" s="3" t="n"/>
+      <c r="AB11" s="3" t="inlineStr">
         <is>
           <t>季报（Tadawul）≈季后4-5周；2026-08-18新增骨架行，数据待回填</t>
         </is>
@@ -1861,17 +1955,25 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
-      <c r="X12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z12" s="9" t="inlineStr">
+      <c r="X12" s="7">
+        <f>SUM(X2:X11)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="8">
+        <f>IF(AND(ISNUMBER(X12),ISNUMBER(P12),P12&lt;&gt;0),(X12-P12)/P12,"-")</f>
+        <v/>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB12" s="9" t="inlineStr">
         <is>
           <t>有数据列直接求和；注意口径混杂（权益/100%合并/湿吨/半年度/财年值），仅作量级参考。俄铝为年度值（计入总计列）；NALCO 为财年值（财年止3月）；South32 财年止6月；印度三家财年止3月</t>
         </is>
@@ -2140,11 +2242,16 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
-      <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="5" t="n"/>
+      <c r="X2" s="4" t="n">
+        <v>246.7</v>
+      </c>
+      <c r="Y2" s="5">
+        <f>IF(AND(ISNUMBER(X2),ISNUMBER(P2),P2&lt;&gt;0),(X2-P2)/P2,"-")</f>
+        <v/>
+      </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>Kwinana 关停/San Ciprián 减产致连年下滑；2026Q2 环比-6%：Pinjarra 运行不稳+飓风 Narelle 气供中断</t>
+          <t>26Q3氧化铝246.7万吨，环比+11%：Pinjarra运行稳定性改善；SEC 8-K EX-99.1</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
@@ -2237,11 +2344,16 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="5" t="n"/>
+      <c r="X3" s="4" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="Y3" s="5">
+        <f>IF(AND(ISNUMBER(X3),ISNUMBER(P3),P3&lt;&gt;0),(X3-P3)/P3,"-")</f>
+        <v/>
+      </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>2026 起 QAL 改按 100% 口径并表+炼厂运行改善（Q1 +6%/Q2 +10%）；2024Q2 -10% 系昆士兰天然气管道破裂冲击 Gladstone</t>
+          <t>26Q3氧化铝207.1万吨，同比+10%/环比+3%；QAL继续100%并表；Rio Q3官方XLSX</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
@@ -2334,11 +2446,16 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="5" t="n"/>
+      <c r="X4" s="4" t="n">
+        <v>149.3</v>
+      </c>
+      <c r="Y4" s="5">
+        <f>IF(AND(ISNUMBER(X4),ISNUMBER(P4),P4&lt;&gt;0),(X4-P4)/P4,"-")</f>
+        <v/>
+      </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>2025Q4 达 1,616kt 超铭牌运行，2026 维持高位（收得率改善+设备稳定）</t>
+          <t>26Q3 Alunorte氧化铝149.3万吨，环比-1%：天然气供应中断造成暂时减产，季内已恢复；Hydro Q3 Report</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -2455,8 +2572,15 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
-      <c r="X5" s="2" t="n"/>
-      <c r="Y5" s="5" t="n"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y5" s="5">
+        <f>IF(AND(ISNUMBER(X5),ISNUMBER(P5),P5&lt;&gt;0),(X5-P5)/P5,"-")</f>
+        <v/>
+      </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>2026H1（8/19 港交所中报）：氧化铝产量 365.8 万吨（+7.6%，增量主要来自 2025-07 收购的印度 Pioneer 氧化铝厂 26% 权益）——半年口径，季度不拆；26Q1 未披露，Q1=Q2=H1/2=182.9 拟合。源：RUSAL 2026 中期业绩（HKEX 2026-08-19）</t>
@@ -2558,11 +2682,16 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="5" t="n"/>
+      <c r="X6" s="4" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="Y6" s="5">
+        <f>IF(AND(ISNUMBER(X6),ISNUMBER(P6),P6&lt;&gt;0),(X6-P6)/P6,"-")</f>
+        <v/>
+      </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>FY26 持平（铝土矿供应改善被 3 月季气旋 Narelle 及第三方天然气中断抵消）；2026-07 宣布随铝资产出售给美铝</t>
+          <t>26Q3 Worsley氧化铝96.6万吨（86%权益），环比+2%：铝土矿供应改善；South32 FY27Q1</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -2677,11 +2806,16 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="5" t="n"/>
+      <c r="X7" s="4" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="Y7" s="5">
+        <f>IF(AND(ISNUMBER(X7),ISNUMBER(P7),P7&lt;&gt;0),(X7-P7)/P7,"-")</f>
+        <v/>
+      </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>FY26 141.1 万吨（超指引 136）</t>
+          <t>26Q3巴西氧化铝34.5万吨（36%权益），环比-2%，炼厂接近铭牌运行；South32 FY27Q1</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -2777,7 +2911,10 @@
       <c r="X8" s="4" t="n">
         <v>89.5</v>
       </c>
-      <c r="Y8" s="5" t="n"/>
+      <c r="Y8" s="5">
+        <f>IF(AND(ISNUMBER(X8),ISNUMBER(P8),P8&lt;&gt;0),(X8-P8)/P8,"-")</f>
+        <v/>
+      </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>Lanjigarh 扩产 2→3.5→5 Mtpa 逐段投产（2025Q4 Train II 投产、2026Q1 同比+104%）</t>
@@ -2866,20 +3003,25 @@
         <f>IF(AND(ISNUMBER(T9),ISNUMBER(N9),N9&lt;&gt;0),(T9-N9)/N9,"-")</f>
         <v/>
       </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V9" s="2" t="n">
+        <v>94.3</v>
       </c>
       <c r="W9" s="5">
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
-      <c r="X9" s="2" t="n"/>
-      <c r="Y9" s="5" t="n"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y9" s="5">
+        <f>IF(AND(ISNUMBER(X9),ISNUMBER(P9),P9&lt;&gt;0),(X9-P9)/P9,"-")</f>
+        <v/>
+      </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>Q1FY27（=26Q2）业绩 8/7 已发：仅披露铝上游出货量 335kt，氧化铝产量未在新闻稿披露 → 未披露。源：Hindalco Q1FY27 业绩新闻稿（2026-08-07）</t>
+          <t>Q1FY27（=26Q2，财年止3月）业绩 2026-08-07 披露：氧化铝总产量（Hydrate as Alumina，含 Utkal）943KT=94.3万吨（同比-2%，Q1FY26=958KT；环比 Q4FY26=931KT +1%）；其中 Utkal 654KT（+1% YoY）；铝上游出货量 335KT、上游 EBITDA 创纪录 ₹7,390cr（+81%）。源：Hindalco Q1FY27 Earnings Presentation p.33（hindalco.com，2026-08-07）</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -2889,7 +3031,7 @@
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>'Hydrate as Alumina'总量（含 Utkal）；财年止3月；个别季度前后版本有±1-2kt 重列；2026Q2 未披露（预计 8 月中）</t>
+          <t>'Hydrate as Alumina'总量（含 Utkal）；财年止3月；个别季度前后版本有±1-2kt 重列；26Q2=94.3已按 Q1FY27 官方演示稿入库（2026-10-14）</t>
         </is>
       </c>
     </row>
@@ -3002,8 +3144,15 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
-      <c r="X10" s="2" t="n"/>
-      <c r="Y10" s="5" t="n"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y10" s="5">
+        <f>IF(AND(ISNUMBER(X10),ISNUMBER(P10),P10&lt;&gt;0),(X10-P10)/P10,"-")</f>
+        <v/>
+      </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>Q1FY27(=26Q2)：煅烧氧化铝57.7万吨（创Q1纪录；水合物57.8万吨）；官方新闻稿8/1+演示稿</t>
@@ -3119,8 +3268,15 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" s="2" t="n"/>
-      <c r="Y11" s="5" t="n"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10-27至28)</t>
+        </is>
+      </c>
+      <c r="Y11" s="5">
+        <f>IF(AND(ISNUMBER(X11),ISNUMBER(P11),P11&lt;&gt;0),(X11-P11)/P11,"-")</f>
+        <v/>
+      </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/27)：H1冶金级氧化铝738万吨(-14.19%)−26Q1 405=333（推算）；另精细氧化铝H1 234万吨(+12.5%)</t>
@@ -3246,8 +3402,15 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
-      <c r="X12" s="2" t="n"/>
-      <c r="Y12" s="5" t="n"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y12" s="5">
+        <f>IF(AND(ISNUMBER(X12),ISNUMBER(P12),P12&lt;&gt;0),(X12-P12)/P12,"-")</f>
+        <v/>
+      </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/21港交所)仅销量口径：氧化铝销量691.7万吨(H1,+8.6%)；产量年报才披露</t>
@@ -3367,8 +3530,15 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
-      <c r="X13" s="2" t="n"/>
-      <c r="Y13" s="5" t="n"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y13" s="5">
+        <f>IF(AND(ISNUMBER(X13),ISNUMBER(P13),P13&lt;&gt;0),(X13-P13)/P13,"-")</f>
+        <v/>
+      </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/27)：H1氧化铝产量65万吨(-3%)；Q1未单独披露,记H1累计</t>
@@ -3488,8 +3658,15 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
-      <c r="X14" s="2" t="n"/>
-      <c r="Y14" s="5" t="n"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y14" s="5">
+        <f>IF(AND(ISNUMBER(X14),ISNUMBER(P14),P14&lt;&gt;0),(X14-P14)/P14,"-")</f>
+        <v/>
+      </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/18)：H1氧化铝产量126.23万吨(+5%)</t>
@@ -3616,7 +3793,10 @@
         <v/>
       </c>
       <c r="X15" s="2" t="n"/>
-      <c r="Y15" s="5" t="n"/>
+      <c r="Y15" s="5">
+        <f>IF(AND(ISNUMBER(X15),ISNUMBER(P15),P15&lt;&gt;0),(X15-P15)/P15,"-")</f>
+        <v/>
+      </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>2023 产量翻倍系滨州二期 400kt 投产+超产（利用率 128.8%）</t>
@@ -3746,8 +3926,15 @@
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
-      <c r="X16" s="2" t="n"/>
-      <c r="Y16" s="5" t="n"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y16" s="5">
+        <f>IF(AND(ISNUMBER(X16),ISNUMBER(P16),P16&lt;&gt;0),(X16-P16)/P16,"-")</f>
+        <v/>
+      </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
           <t>Ma'aden Q2 2026 已披露，但 Ras Al Khair 氧化铝分季产量未见公开披露（二手源 vision2030 称某季 47.8 万吨，口径待核）→ 未找到。源：Ma'aden Q2 2026 / AlCircle</t>
@@ -3856,8 +4043,14 @@
         <f>IF(AND(ISNUMBER(V17),ISNUMBER(O17),O17&lt;&gt;0),(V17-O17)/O17,"-")</f>
         <v/>
       </c>
-      <c r="X17" s="7" t="n"/>
-      <c r="Y17" s="8" t="n"/>
+      <c r="X17" s="7">
+        <f>SUM(X2:X16)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="8">
+        <f>IF(AND(ISNUMBER(X17),ISNUMBER(P17),P17&lt;&gt;0),(X17-P17)/P17,"-")</f>
+        <v/>
+      </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
           <t>-</t>
@@ -4137,11 +4330,16 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
-      <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="5" t="n"/>
+      <c r="X2" s="4" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="Y2" s="5">
+        <f>IF(AND(ISNUMBER(X2),ISNUMBER(P2),P2&lt;&gt;0),(X2-P2)/P2,"-")</f>
+        <v/>
+      </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>San Ciprián（2026-04 重启完成）/Alumar/Lista/Portland 重启推动连增，2026Q2 636kt 环比+5%</t>
+          <t>26Q3原铝64.9万吨，环比+2%：前期重启产能贡献+Alumar重启完成；SEC 8-K EX-99.1</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
@@ -4234,11 +4432,16 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="5" t="n"/>
+      <c r="X3" s="4" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="Y3" s="5">
+        <f>IF(AND(ISNUMBER(X3),ISNUMBER(P3),P3&lt;&gt;0),(X3-P3)/P3,"-")</f>
+        <v/>
+      </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>2025 +3% 至指引上限（NZAS 爬坡完成）；2026H1 基本持平</t>
+          <t>26Q3原铝84.2万吨，同比-2%/环比持平；Rio Q3官方XLSX</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
@@ -4331,11 +4534,16 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="5" t="n"/>
+      <c r="X4" s="4" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="Y4" s="5">
+        <f>IF(AND(ISNUMBER(X4),ISNUMBER(P4),P4&lt;&gt;0),(X4-P4)/P4,"-")</f>
+        <v/>
+      </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>2026Q2 -3%：Qatalum 自 2026-03 起因供气受限维持约60%开工的完整季度影响，部分被挪威爬坡抵消</t>
+          <t>26Q3原铝50.3万吨，环比+1%：挪威液态金属产量创纪录，Slovalco 8月底开始重启；Hydro Q3 Report</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -4452,8 +4660,15 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
-      <c r="X5" s="2" t="n"/>
-      <c r="Y5" s="5" t="n"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y5" s="5">
+        <f>IF(AND(ISNUMBER(X5),ISNUMBER(P5),P5&lt;&gt;0),(X5-P5)/P5,"-")</f>
+        <v/>
+      </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>2026H1（8/19 港交所中报）：原铝产量 2.010 百万吨（+4.5%）——半年口径，季度不拆。源：RUSAL 2026 中期业绩（HKEX 2026-08-19）</t>
@@ -4565,11 +4780,16 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="5" t="n"/>
+      <c r="X6" s="4" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y6" s="5">
+        <f>IF(AND(ISNUMBER(X6),ISNUMBER(P6),P6&lt;&gt;0),(X6-P6)/P6,"-")</f>
+        <v/>
+      </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>持续测试最大技术产能，FY26 受南非限电（load-shedding）影响</t>
+          <t>26Q3 Hillside原铝17.7万吨，环比-1%：限电下继续测试最大技术产能；South32 FY27Q1</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -4686,11 +4906,16 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="5" t="n"/>
+      <c r="X7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="5">
+        <f>IF(AND(ISNUMBER(X7),ISNUMBER(P7),P7&lt;&gt;0),(X7-P7)/P7,"-")</f>
+        <v/>
+      </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15 电力协议到期未续约，转入维护保养（care &amp; maintenance），2026Q2 产量为 0</t>
+          <t>26Q3 Mozal产量0：2026-03起维护保养；South32 FY27Q1</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -4811,11 +5036,16 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="5" t="n"/>
+      <c r="X8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="5">
+        <f>IF(AND(ISNUMBER(X8),ISNUMBER(P8),P8&lt;&gt;0),(X8-P8)/P8,"-")</f>
+        <v/>
+      </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>FY25 +33%（三条电解槽线复产爬坡），FY26 +4%（爬坡完成）</t>
+          <t>26Q3巴西电解铝4.0万吨（40%权益），环比+8%：季末全部电解槽运行；South32 FY27Q1</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -4911,7 +5141,10 @@
       <c r="X9" s="4" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="Y9" s="5" t="n"/>
+      <c r="Y9" s="5">
+        <f>IF(AND(ISNUMBER(X9),ISNUMBER(P9),P9&lt;&gt;0),(X9-P9)/P9,"-")</f>
+        <v/>
+      </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>基本满产稳定；2026Q2 创历史最高季度（BALCO 新建 525kA 电解槽系列投产贡献）</t>
@@ -5007,8 +5240,15 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
-      <c r="X10" s="2" t="n"/>
-      <c r="Y10" s="5" t="n"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y10" s="5">
+        <f>IF(AND(ISNUMBER(X10),ISNUMBER(P10),P10&lt;&gt;0),(X10-P10)/P10,"-")</f>
+        <v/>
+      </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>Q1FY27（=26Q2）铝上游出货量 335kt=33.5 万吨（同比+3%，出货量口径）；上游 EBITDA 创纪录 ₹7,390  crore（+81%）；Aditya 二期 FY28 投产。源：Hindalco Q1FY27 业绩新闻稿（2026-08-07）</t>
@@ -5132,8 +5372,15 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" s="2" t="n"/>
-      <c r="Y11" s="5" t="n"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y11" s="5">
+        <f>IF(AND(ISNUMBER(X11),ISNUMBER(P11),P11&lt;&gt;0),(X11-P11)/P11,"-")</f>
+        <v/>
+      </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>Q1FY27(=26Q2)：电解铝11.6万吨（上年同季11.5）；官方演示稿</t>
@@ -5249,8 +5496,15 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
-      <c r="X12" s="2" t="n"/>
-      <c r="Y12" s="5" t="n"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10-27至28)</t>
+        </is>
+      </c>
+      <c r="Y12" s="5">
+        <f>IF(AND(ISNUMBER(X12),ISNUMBER(P12),P12&lt;&gt;0),(X12-P12)/P12,"-")</f>
+        <v/>
+      </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/27)：H1原铝(含合金)402万吨(+1.26%)−26Q1 201=201（推算）</t>
@@ -5374,8 +5628,15 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
-      <c r="X13" s="2" t="n"/>
-      <c r="Y13" s="5" t="n"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y13" s="5">
+        <f>IF(AND(ISNUMBER(X13),ISNUMBER(P13),P13&lt;&gt;0),(X13-P13)/P13,"-")</f>
+        <v/>
+      </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/21港交所)仅销量口径：铝合金产品销量281.1万吨(H1,-3.3%)、深加工44.4万吨(+23.2%)；产量年报才披露</t>
@@ -5499,8 +5760,15 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
-      <c r="X14" s="2" t="n"/>
-      <c r="Y14" s="5" t="n"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y14" s="5">
+        <f>IF(AND(ISNUMBER(X14),ISNUMBER(P14),P14&lt;&gt;0),(X14-P14)/P14,"-")</f>
+        <v/>
+      </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
           <t>2026中报(7/27)仅定性'满产满销,时间过半任务过半'（产能170万吨/年），无吨数；另披露铝箔6.38万吨(+20%)</t>
@@ -5620,8 +5888,15 @@
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
         <v/>
       </c>
-      <c r="X15" s="2" t="n"/>
-      <c r="Y15" s="5" t="n"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y15" s="5">
+        <f>IF(AND(ISNUMBER(X15),ISNUMBER(P15),P15&lt;&gt;0),(X15-P15)/P15,"-")</f>
+        <v/>
+      </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/27)：H1铝产品(铝商品口径,含合金及加工)162万吨(约+1%)；全年目标319万吨完成50.8%</t>
@@ -5741,8 +6016,15 @@
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
-      <c r="X16" s="2" t="n"/>
-      <c r="Y16" s="5" t="n"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y16" s="5">
+        <f>IF(AND(ISNUMBER(X16),ISNUMBER(P16),P16&lt;&gt;0),(X16-P16)/P16,"-")</f>
+        <v/>
+      </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
           <t>2026中报(8/18)：H1电解铝66.05万吨(+12.8%,140万吨技改项目爬产,下半年还有增量)</t>
@@ -5869,7 +6151,10 @@
         <v/>
       </c>
       <c r="X17" s="2" t="n"/>
-      <c r="Y17" s="5" t="n"/>
+      <c r="Y17" s="5">
+        <f>IF(AND(ISNUMBER(X17),ISNUMBER(P17),P17&lt;&gt;0),(X17-P17)/P17,"-")</f>
+        <v/>
+      </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
           <t>产能利用率 94-96%，稳定在 75 万吨级</t>
@@ -5993,8 +6278,15 @@
         <f>IF(AND(ISNUMBER(V18),ISNUMBER(O18),O18&lt;&gt;0),(V18-O18)/O18,"-")</f>
         <v/>
       </c>
-      <c r="X18" s="2" t="n"/>
-      <c r="Y18" s="5" t="n"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y18" s="5">
+        <f>IF(AND(ISNUMBER(X18),ISNUMBER(P18),P18&lt;&gt;0),(X18-P18)/P18,"-")</f>
+        <v/>
+      </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
           <t>安哥拉年产 12 万吨电解铝项目 2026 年 1 月正式投产试运行</t>
@@ -6124,8 +6416,15 @@
         <f>IF(AND(ISNUMBER(V19),ISNUMBER(O19),O19&lt;&gt;0),(V19-O19)/O19,"-")</f>
         <v/>
       </c>
-      <c r="X19" s="2" t="n"/>
-      <c r="Y19" s="5" t="n"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y19" s="5">
+        <f>IF(AND(ISNUMBER(X19),ISNUMBER(P19),P19&lt;&gt;0),(X19-P19)/P19,"-")</f>
+        <v/>
+      </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
           <t>季报不披露产量吨数（2026Q1/Q2季报均已核验,仅财务口径；26Q2核心净利+42%）；产能锚点1.08Mtpa</t>
@@ -6227,8 +6526,15 @@
         <f>IF(AND(ISNUMBER(V20),ISNUMBER(O20),O20&lt;&gt;0),(V20-O20)/O20,"-")</f>
         <v/>
       </c>
-      <c r="X20" s="2" t="n"/>
-      <c r="Y20" s="5" t="n"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待发布(2026-11-05)</t>
+        </is>
+      </c>
+      <c r="Y20" s="5">
+        <f>IF(AND(ISNUMBER(X20),ISNUMBER(P20),P20&lt;&gt;0),(X20-P20)/P20,"-")</f>
+        <v/>
+      </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
           <t>26Q2 出货量 130,632 吨=13.06 万吨（环比+6%：Mt. Holly 最后 90 槽重启完成+Grundartangi 2 号线恢复近满产）。源：Century Q2 2026 业绩（8-K ex99.1）</t>
@@ -6354,8 +6660,15 @@
         <f>IF(AND(ISNUMBER(V21),ISNUMBER(O21),O21&lt;&gt;0),(V21-O21)/O21,"-")</f>
         <v/>
       </c>
-      <c r="X21" s="2" t="n"/>
-      <c r="Y21" s="5" t="n"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y21" s="5">
+        <f>IF(AND(ISNUMBER(X21),ISNUMBER(P21),P21&lt;&gt;0),(X21-P21)/P21,"-")</f>
+        <v/>
+      </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
           <t>26Q2 净成品铝产量 155,469 吨=15.55 万吨（同比-61%：地区紧张局势对 1/2/3 号线控制性停产）；销量 280,799 吨（-32%）。源：Alba Q2/H1 2026 业绩（2026-08-04）</t>
@@ -6477,8 +6790,15 @@
         <f>IF(AND(ISNUMBER(V22),ISNUMBER(O22),O22&lt;&gt;0),(V22-O22)/O22,"-")</f>
         <v/>
       </c>
-      <c r="X22" s="2" t="n"/>
-      <c r="Y22" s="5" t="n"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y22" s="5">
+        <f>IF(AND(ISNUMBER(X22),ISNUMBER(P22),P22&lt;&gt;0),(X22-P22)/P22,"-")</f>
+        <v/>
+      </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
           <t>26Q2 原铝 242,000 吨=24.2 万吨（环比微降）；铝板块收入 +49% 至 $1.01bn（均价+51%）。26Q1=24.9 为二手源（vision2030，待核）。源：Ma'aden Q2 2026（Tadawul，8 月上旬）/AlCircle</t>
@@ -6587,8 +6907,14 @@
         <f>IF(AND(ISNUMBER(V23),ISNUMBER(O23),O23&lt;&gt;0),(V23-O23)/O23,"-")</f>
         <v/>
       </c>
-      <c r="X23" s="7" t="n"/>
-      <c r="Y23" s="8" t="n"/>
+      <c r="X23" s="7">
+        <f>SUM(X2:X22)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="8">
+        <f>IF(AND(ISNUMBER(X23),ISNUMBER(P23),P23&lt;&gt;0),(X23-P23)/P23,"-")</f>
+        <v/>
+      </c>
       <c r="Z23" s="6" t="inlineStr">
         <is>
           <t>-</t>
@@ -6616,7 +6942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6794,6 +7120,57 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>26Q2复核：天山铝土矿——2026中报(8/25)复核确认无开采量绝对值，保持空缺；神火电解铝中报仅"满产满销"定性无吨数（8/31已记），维持空缺</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>天山铝业/神火股份2026半年度报告全文（新浪财经/巨潮）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>铝 26Q2 缺口收口：Hindalco 氧化铝 26Q2=94.3万吨（Q1FY27 官方演示稿 p.33：Alumina incl Utkal 943KT，-2% YoY；Utkal 654KT +1%）——此前 8/24 仅据新闻稿标'未披露'，演示稿实际有产量；电解铝 26Q2=33.5（出货量口径）维持不变</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hindalco Q1FY27 Earnings Presentation（hindalco.com/Upload/PDF/hindalco-investor-presentation-q1fy27.pdf，2026-08-07）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>铝26Q3第一批：美铝(矿930/氧246.7/铝64.9)、力拓(1574.5/207.1/84.2)、海德鲁(241.0/149.3/50.3)、South32(Worsley 96.6/巴西氧34.5/Hillside 17.7/巴西铝4.0/Mozal 0)入库；其余按披露日历标待发布或无季度披露</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Alcoa 8-K EX-99.1 10/15；Rio Tinto Q3 Operations Review+官方XLSX 10/14；Hydro Q3 Report 10/23；South32 September Quarterly Report 10/19；Century/Hindalco/NALCO披露日历</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
